--- a/docs/lab3/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/lab3/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2CF288-1087-4406-B06B-62FB5E417926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843BE698-1AAE-450F-8C5F-524171407950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="140">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -599,6 +599,18 @@
   </si>
   <si>
     <t>list(ingredient cu cantitate = 1, size n+1)</t>
+  </si>
+  <si>
+    <t>F02_TC11</t>
+  </si>
+  <si>
+    <t>(1, null)</t>
+  </si>
+  <si>
+    <t>exception: ingrediente null</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -806,7 +818,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1211,17 +1223,6 @@
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1304,9 +1305,96 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1322,129 +1410,84 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1457,53 +1500,11 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1581,8 +1582,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>20264</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="13" name="Ink 12">
@@ -1601,7 +1602,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="13" name="Ink 12">
@@ -2014,12 +2015,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="56"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="33" t="s">
@@ -2156,62 +2157,62 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="71"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="78"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="56"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="71"/>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="Q6" s="54" t="s">
+      <c r="Q6" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="81" t="s">
+      <c r="C8" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
       <c r="F8" s="27"/>
       <c r="G8" s="27"/>
       <c r="I8" s="8"/>
-      <c r="Q8" s="68" t="s">
+      <c r="Q8" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="68"/>
-      <c r="S8" s="68"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="89"/>
       <c r="T8" s="28">
         <v>6</v>
       </c>
@@ -2220,19 +2221,19 @@
       <c r="B9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="I9" s="32"/>
-      <c r="Q9" s="68" t="s">
+      <c r="Q9" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="68"/>
-      <c r="S9" s="68"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
       <c r="T9" s="28">
         <v>6</v>
       </c>
@@ -2241,27 +2242,27 @@
       <c r="B10" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
       <c r="F10" s="30"/>
       <c r="G10" s="30"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="73"/>
-      <c r="O10" s="74"/>
-      <c r="Q10" s="68" t="s">
+      <c r="I10" s="80"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="82"/>
+      <c r="Q10" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="R10" s="68" t="s">
+      <c r="R10" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="S10" s="68"/>
+      <c r="S10" s="89"/>
       <c r="T10" s="28">
         <v>6</v>
       </c>
@@ -2270,300 +2271,303 @@
       <c r="B11" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C11" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="76"/>
-      <c r="O11" s="77"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="85"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="76"/>
-      <c r="O12" s="77"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="85"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="77"/>
-      <c r="Q13" s="54" t="s">
+      <c r="I13" s="83"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="85"/>
+      <c r="Q13" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="76"/>
-      <c r="O14" s="77"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="85"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="75"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="77"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="85"/>
       <c r="Q15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="R15" s="81" t="s">
+      <c r="R15" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
+      <c r="S15" s="90"/>
+      <c r="T15" s="90"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="75"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="77"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="85"/>
       <c r="Q16" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="R16" s="91" t="s">
+      <c r="R16" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="S16" s="92"/>
-      <c r="T16" s="93"/>
+      <c r="S16" s="74"/>
+      <c r="T16" s="75"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="75"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="77"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="85"/>
       <c r="Q17" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="R17" s="66" t="s">
+      <c r="R17" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="75"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="77"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="85"/>
       <c r="Q18" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="R18" s="91" t="s">
+      <c r="R18" s="73" t="s">
         <v>101</v>
       </c>
-      <c r="S18" s="92"/>
-      <c r="T18" s="93"/>
+      <c r="S18" s="74"/>
+      <c r="T18" s="75"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="75"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="77"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="85"/>
       <c r="Q19" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="R19" s="91" t="s">
+      <c r="R19" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="S19" s="92"/>
-      <c r="T19" s="93"/>
+      <c r="S19" s="74"/>
+      <c r="T19" s="75"/>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="75"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="77"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="85"/>
       <c r="Q20" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="R20" s="91" t="s">
+      <c r="R20" s="73" t="s">
         <v>119</v>
       </c>
-      <c r="S20" s="92"/>
-      <c r="T20" s="93"/>
+      <c r="S20" s="74"/>
+      <c r="T20" s="75"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="75"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="77"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="85"/>
       <c r="Q21" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="R21" s="91" t="s">
+      <c r="R21" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="S21" s="92"/>
-      <c r="T21" s="93"/>
+      <c r="S21" s="74"/>
+      <c r="T21" s="75"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="75"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="77"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="85"/>
       <c r="Q22" s="29"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="75"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="77"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="85"/>
       <c r="Q23" s="29"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="78"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="80"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="87"/>
+      <c r="O24" s="88"/>
       <c r="Q24" s="29"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="Q25" s="29"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="Q26" s="29"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="Q27" s="29"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+      <c r="T27" s="72"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="Q28" s="29"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="Q29" s="29"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="Q30" s="29"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="R25:T25"/>
-    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R21:T21"/>
@@ -2576,18 +2580,15 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="R29:T29"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="R26:T26"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2627,12 +2628,12 @@
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="56"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B3" s="31" t="s">
@@ -2646,153 +2647,153 @@
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="88" t="s">
+      <c r="E6" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
-      <c r="S6" s="88"/>
-      <c r="T6" s="88"/>
-      <c r="U6" s="88"/>
-      <c r="V6" s="88"/>
-      <c r="W6" s="88"/>
-      <c r="X6" s="88"/>
-      <c r="Y6" s="88"/>
-      <c r="Z6" s="88"/>
-      <c r="AA6" s="88"/>
-      <c r="AB6" s="88"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
     </row>
     <row r="7" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="88"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="85" t="s">
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="84" t="s">
+      <c r="F7" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
-      <c r="N7" s="84"/>
-      <c r="O7" s="84"/>
-      <c r="P7" s="86" t="s">
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="98"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="86"/>
-      <c r="R7" s="86"/>
-      <c r="S7" s="86"/>
-      <c r="T7" s="86"/>
-      <c r="U7" s="86"/>
-      <c r="V7" s="87" t="s">
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="95"/>
+      <c r="U7" s="95"/>
+      <c r="V7" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="W7" s="87"/>
-      <c r="X7" s="87"/>
-      <c r="Y7" s="87"/>
-      <c r="Z7" s="87"/>
-      <c r="AA7" s="87"/>
-      <c r="AB7" s="87"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="94"/>
+      <c r="Z7" s="94"/>
+      <c r="AA7" s="94"/>
+      <c r="AB7" s="94"/>
     </row>
     <row r="8" spans="2:28" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="88"/>
-      <c r="C8" s="82" t="s">
+      <c r="B8" s="91"/>
+      <c r="C8" s="96" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="82" t="s">
+      <c r="D8" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="84" t="s">
+      <c r="E8" s="99"/>
+      <c r="F8" s="98" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84" t="s">
+      <c r="G8" s="98"/>
+      <c r="H8" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="84"/>
-      <c r="J8" s="84" t="s">
+      <c r="I8" s="98"/>
+      <c r="J8" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84" t="s">
+      <c r="K8" s="98"/>
+      <c r="L8" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="84"/>
-      <c r="N8" s="84" t="s">
+      <c r="M8" s="98"/>
+      <c r="N8" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="O8" s="84"/>
-      <c r="P8" s="86" t="s">
+      <c r="O8" s="98"/>
+      <c r="P8" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="Q8" s="86" t="s">
+      <c r="Q8" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="R8" s="86" t="s">
+      <c r="R8" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="86" t="s">
+      <c r="S8" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="T8" s="86" t="s">
+      <c r="T8" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="U8" s="86" t="s">
+      <c r="U8" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="V8" s="87">
+      <c r="V8" s="94">
         <v>0</v>
       </c>
-      <c r="W8" s="87">
+      <c r="W8" s="94">
         <v>1</v>
       </c>
-      <c r="X8" s="87">
+      <c r="X8" s="94">
         <v>2</v>
       </c>
-      <c r="Y8" s="87" t="s">
+      <c r="Y8" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="Z8" s="87" t="s">
+      <c r="Z8" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="AA8" s="87" t="s">
+      <c r="AA8" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="AB8" s="87" t="s">
+      <c r="AB8" s="94" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="88"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="85"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="99"/>
       <c r="F9" s="9" t="s">
         <v>46</v>
       </c>
@@ -2823,19 +2824,19 @@
       <c r="O9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="86"/>
-      <c r="R9" s="86"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="86"/>
-      <c r="U9" s="86"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="87"/>
-      <c r="X9" s="87"/>
-      <c r="Y9" s="87"/>
-      <c r="Z9" s="87"/>
-      <c r="AA9" s="87"/>
-      <c r="AB9" s="87"/>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
+      <c r="S9" s="95"/>
+      <c r="T9" s="95"/>
+      <c r="U9" s="95"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="94"/>
+      <c r="AA9" s="94"/>
+      <c r="AB9" s="94"/>
     </row>
     <row r="10" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
@@ -3333,17 +3334,76 @@
       </c>
       <c r="AB19" s="15"/>
     </row>
-    <row r="20" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="94"/>
+    <row r="20" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="O20" s="13"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15"/>
+      <c r="AB20" s="15"/>
     </row>
     <row r="21" spans="2:28" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="94"/>
-      <c r="C21" s="95" t="s">
+      <c r="B21" s="35"/>
+      <c r="C21" s="36" t="s">
         <v>123</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:U7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C7"/>
@@ -3360,19 +3420,6 @@
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="V7:AB7"/>
     <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:U7"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3400,46 +3447,46 @@
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="62"/>
-      <c r="G4" s="60" t="s">
+      <c r="F4" s="50"/>
+      <c r="G4" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="61"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="59"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="65"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="54"/>
       <c r="E5" s="2" t="s">
         <v>126</v>
       </c>
@@ -3457,16 +3504,16 @@
       <c r="B6" s="16">
         <v>16</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="100" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="100">
+      <c r="E6" s="39">
         <v>1</v>
       </c>
-      <c r="F6" s="100" t="s">
+      <c r="F6" s="39" t="s">
         <v>128</v>
       </c>
       <c r="G6" s="11" t="s">
@@ -3480,14 +3527,14 @@
       <c r="B7" s="16">
         <v>17</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="98">
+      <c r="E7" s="37">
         <v>0</v>
       </c>
-      <c r="F7" s="101" t="s">
+      <c r="F7" s="40" t="s">
         <v>128</v>
       </c>
       <c r="G7" s="11" t="s">
@@ -3501,14 +3548,14 @@
       <c r="B8" s="16">
         <v>18</v>
       </c>
-      <c r="C8" s="97"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="98">
+      <c r="E8" s="37">
         <v>1</v>
       </c>
-      <c r="F8" s="101" t="s">
+      <c r="F8" s="40" t="s">
         <v>129</v>
       </c>
       <c r="G8" s="11" t="s">
@@ -3522,14 +3569,14 @@
       <c r="B9" s="16">
         <v>19</v>
       </c>
-      <c r="C9" s="97"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="98">
+      <c r="E9" s="37">
         <v>1</v>
       </c>
-      <c r="F9" s="101" t="s">
+      <c r="F9" s="40" t="s">
         <v>130</v>
       </c>
       <c r="G9" s="11" t="s">
@@ -3543,14 +3590,14 @@
       <c r="B10" s="16">
         <v>20</v>
       </c>
-      <c r="C10" s="97"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="98">
+      <c r="E10" s="37">
         <v>0</v>
       </c>
-      <c r="F10" s="101" t="s">
+      <c r="F10" s="40" t="s">
         <v>129</v>
       </c>
       <c r="G10" s="11" t="s">
@@ -3564,14 +3611,14 @@
       <c r="B11" s="16">
         <v>21</v>
       </c>
-      <c r="C11" s="97"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="98">
+      <c r="E11" s="37">
         <v>1</v>
       </c>
-      <c r="F11" s="101" t="s">
+      <c r="F11" s="40" t="s">
         <v>132</v>
       </c>
       <c r="G11" s="11" t="s">
@@ -3585,14 +3632,14 @@
       <c r="B12" s="16">
         <v>22</v>
       </c>
-      <c r="C12" s="97"/>
+      <c r="C12" s="101"/>
       <c r="D12" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="98">
+      <c r="E12" s="37">
         <v>1</v>
       </c>
-      <c r="F12" s="101" t="s">
+      <c r="F12" s="40" t="s">
         <v>131</v>
       </c>
       <c r="G12" s="11" t="s">
@@ -3606,14 +3653,14 @@
       <c r="B13" s="16">
         <v>23</v>
       </c>
-      <c r="C13" s="97"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="98">
+      <c r="E13" s="37">
         <v>1</v>
       </c>
-      <c r="F13" s="101" t="s">
+      <c r="F13" s="40" t="s">
         <v>133</v>
       </c>
       <c r="G13" s="11" t="s">
@@ -3627,14 +3674,14 @@
       <c r="B14" s="16">
         <v>24</v>
       </c>
-      <c r="C14" s="97"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E14" s="98">
+      <c r="E14" s="37">
         <v>1</v>
       </c>
-      <c r="F14" s="101" t="s">
+      <c r="F14" s="40" t="s">
         <v>134</v>
       </c>
       <c r="G14" s="11" t="s">
@@ -3648,14 +3695,14 @@
       <c r="B15" s="16">
         <v>25</v>
       </c>
-      <c r="C15" s="97"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="99">
+      <c r="E15" s="38">
         <v>1</v>
       </c>
-      <c r="F15" s="101" t="s">
+      <c r="F15" s="40" t="s">
         <v>135</v>
       </c>
       <c r="G15" s="11" t="s">
@@ -3665,7 +3712,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:8" ht="31.8" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="16">
+        <v>26</v>
+      </c>
+      <c r="C16" s="101"/>
+      <c r="D16" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="37">
+        <v>1</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
         <v>59</v>
@@ -3673,61 +3740,61 @@
       <c r="G21" s="17"/>
     </row>
     <row r="22" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
       <c r="F22" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="47"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="52" t="s">
+      <c r="G22" s="42"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="J22" s="53"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="H23" s="49" t="s">
+      <c r="H23" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="I23" s="51" t="s">
+      <c r="I23" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="J23" s="43" t="s">
+      <c r="J23" s="51" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="41"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="55"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="21">
@@ -3756,6 +3823,17 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I22:J22"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="B3:H3"/>
@@ -3764,18 +3842,7 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="C6:C15"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C6:C16"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3973,15 +4040,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
@@ -3990,6 +4048,15 @@
     <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4012,14 +4079,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4028,4 +4087,12 @@
     <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>